--- a/03_Group_comparisons/Proteome_T1/c_data/03_set_contrasts.xlsx
+++ b/03_Group_comparisons/Proteome_T1/c_data/03_set_contrasts.xlsx
@@ -8789,7 +8789,7 @@
     <t>03_Group_comparisons/Proteome_T1/c_data/02_fit.rds</t>
   </si>
   <si>
-    <t>1da66a2ac24edc0397bd526c216af2a7</t>
+    <t>f242ce575d214144e78b086d4875604f</t>
   </si>
   <si>
     <t>design</t>
@@ -8798,13 +8798,13 @@
     <t>03_Group_comparisons/Proteome_T1/c_data/01_design.rds</t>
   </si>
   <si>
-    <t>35e9ac543e6ba7b4cdc0cdce760f6b50</t>
+    <t>d1c841970f30ae338d5be96c625de913</t>
   </si>
   <si>
     <t>01_Processing/03_Quantification/c_data/DAList_limpa.rds</t>
   </si>
   <si>
-    <t>268362b9975bc00d3bc3b85b0f5736f7</t>
+    <t>015331bb453caea36bcabbe182b7eac6</t>
   </si>
   <si>
     <t>singscore</t>
@@ -8822,7 +8822,7 @@
     <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
-    <t>5a1989db406daa0b70189a9f0df52cf3</t>
+    <t>cdb8d908fb24ab0d2be6f2d00021db81</t>
   </si>
   <si>
     <t>BiocGenerics</t>
